--- a/data/final/05_merged_crs_gsynth.xlsx
+++ b/data/final/05_merged_crs_gsynth.xlsx
@@ -394,19 +394,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.03094295618166015</v>
+        <v>-0.03094295618166065</v>
       </c>
       <c r="C2">
-        <v>0.6241826490301035</v>
+        <v>0.6370177862774107</v>
       </c>
       <c r="D2">
-        <v>0.06315776983463536</v>
+        <v>0.06557482180721773</v>
       </c>
       <c r="E2">
-        <v>-0.1547299104014156</v>
+        <v>-0.1594672452164391</v>
       </c>
       <c r="F2">
-        <v>0.09284399803809536</v>
+        <v>0.09758133285311779</v>
       </c>
     </row>
     <row r="3">
@@ -416,19 +416,19 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.03094295618166005</v>
+        <v>-0.03094295618166047</v>
       </c>
       <c r="C3">
-        <v>0.6241826490301043</v>
+        <v>0.6370177862774127</v>
       </c>
       <c r="D3">
-        <v>0.06315776983463532</v>
+        <v>0.06557482180721773</v>
       </c>
       <c r="E3">
-        <v>-0.1547299104014155</v>
+        <v>-0.1594672452164389</v>
       </c>
       <c r="F3">
-        <v>0.09284399803809537</v>
+        <v>0.09758133285311797</v>
       </c>
     </row>
     <row r="4">
@@ -438,19 +438,19 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.006877460534914774</v>
+        <v>0.006877460534914032</v>
       </c>
       <c r="C4">
-        <v>0.911970323868972</v>
+        <v>0.9157771777812036</v>
       </c>
       <c r="D4">
-        <v>0.06220927206817043</v>
+        <v>0.0650323512938924</v>
       </c>
       <c r="E4">
-        <v>-0.1150504722231528</v>
+        <v>-0.1205836058310718</v>
       </c>
       <c r="F4">
-        <v>0.1288053932929824</v>
+        <v>0.1343385269008999</v>
       </c>
     </row>
     <row r="5">
@@ -460,19 +460,19 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.005971754394383524</v>
+        <v>0.005971754394382613</v>
       </c>
       <c r="C5">
-        <v>0.9271860466024107</v>
+        <v>0.9290222491000513</v>
       </c>
       <c r="D5">
-        <v>0.0653466355595046</v>
+        <v>0.06704181460167304</v>
       </c>
       <c r="E5">
-        <v>-0.1221052978131099</v>
+        <v>-0.125427787683108</v>
       </c>
       <c r="F5">
-        <v>0.1340488066018769</v>
+        <v>0.1373712964718732</v>
       </c>
     </row>
     <row r="6">
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.1126027365027691</v>
+        <v>-0.1126027365027698</v>
       </c>
       <c r="C6">
-        <v>0.1037183268790824</v>
+        <v>0.09174965326231854</v>
       </c>
       <c r="D6">
-        <v>0.06920505200181373</v>
+        <v>0.06677742260143854</v>
       </c>
       <c r="E6">
-        <v>-0.2482421459745455</v>
+        <v>-0.2434840797820003</v>
       </c>
       <c r="F6">
-        <v>0.02303667296900738</v>
+        <v>0.01827860677646068</v>
       </c>
     </row>
     <row r="7">
@@ -504,19 +504,19 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.1162515653252542</v>
+        <v>-0.1162515653252551</v>
       </c>
       <c r="C7">
-        <v>0.1620144176192087</v>
+        <v>0.1529466194858393</v>
       </c>
       <c r="D7">
-        <v>0.083136085849759</v>
+        <v>0.08134027861382476</v>
       </c>
       <c r="E7">
-        <v>-0.2791952994064118</v>
+        <v>-0.2756755819008051</v>
       </c>
       <c r="F7">
-        <v>0.04669216875590337</v>
+        <v>0.04317245125029498</v>
       </c>
     </row>
     <row r="8">
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.1264118477735243</v>
+        <v>-0.1264118477735251</v>
       </c>
       <c r="C8">
-        <v>0.1889444224752395</v>
+        <v>0.1786436462099312</v>
       </c>
       <c r="D8">
-        <v>0.09622521071533263</v>
+        <v>0.09399048794716204</v>
       </c>
       <c r="E8">
-        <v>-0.3150097951803539</v>
+        <v>-0.3106298190393087</v>
       </c>
       <c r="F8">
-        <v>0.06218609963330529</v>
+        <v>0.05780612349225844</v>
       </c>
     </row>
     <row r="9">
@@ -548,19 +548,19 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.117867661300818</v>
+        <v>-0.1178676613008188</v>
       </c>
       <c r="C9">
-        <v>0.2126265246032968</v>
+        <v>0.2045471023636309</v>
       </c>
       <c r="D9">
-        <v>0.09456832969957023</v>
+        <v>0.09290407984127873</v>
       </c>
       <c r="E9">
-        <v>-0.3032181815900852</v>
+        <v>-0.2999563118065587</v>
       </c>
       <c r="F9">
-        <v>0.06748285898844908</v>
+        <v>0.0642209892049211</v>
       </c>
     </row>
     <row r="10">
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.02609962545659964</v>
+        <v>0.02609962545659925</v>
       </c>
       <c r="C10">
-        <v>0.6878758998060452</v>
+        <v>0.7158437052138569</v>
       </c>
       <c r="D10">
-        <v>0.06496657304113208</v>
+        <v>0.07169849459010494</v>
       </c>
       <c r="E10">
-        <v>-0.10123251790301</v>
+        <v>-0.1144268416857463</v>
       </c>
       <c r="F10">
-        <v>0.1534317688162093</v>
+        <v>0.1666260925989448</v>
       </c>
     </row>
     <row r="11">
@@ -592,19 +592,19 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.003388677839218529</v>
+        <v>0.003388677839218016</v>
       </c>
       <c r="C11">
-        <v>0.9563778105730747</v>
+        <v>0.9599245326312398</v>
       </c>
       <c r="D11">
-        <v>0.06195071977322875</v>
+        <v>0.06743867380678145</v>
       </c>
       <c r="E11">
-        <v>-0.1180325017326432</v>
+        <v>-0.1287886939872183</v>
       </c>
       <c r="F11">
-        <v>0.1248098574110802</v>
+        <v>0.1355660496656543</v>
       </c>
     </row>
     <row r="12">
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.000716171653610217</v>
+        <v>-0.0007161716536106895</v>
       </c>
       <c r="C12">
-        <v>0.9908464530637904</v>
+        <v>0.9916343759673834</v>
       </c>
       <c r="D12">
-        <v>0.06242495663685352</v>
+        <v>0.06830474731409028</v>
       </c>
       <c r="E12">
-        <v>-0.1230668383983177</v>
+        <v>-0.1345910163623366</v>
       </c>
       <c r="F12">
-        <v>0.1216344950910972</v>
+        <v>0.1331586730551152</v>
       </c>
     </row>
     <row r="13">
@@ -636,19 +636,19 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.04386160229930954</v>
+        <v>0.04386160229930907</v>
       </c>
       <c r="C13">
-        <v>0.4979686900595395</v>
+        <v>0.5261845271238936</v>
       </c>
       <c r="D13">
-        <v>0.06472228504420308</v>
+        <v>0.06919968149294402</v>
       </c>
       <c r="E13">
-        <v>-0.08299174538446384</v>
+        <v>-0.09176728116850408</v>
       </c>
       <c r="F13">
-        <v>0.1707149499830829</v>
+        <v>0.1794904857671222</v>
       </c>
     </row>
     <row r="14">
@@ -658,19 +658,19 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.1646098748311106</v>
+        <v>0.1646098748311101</v>
       </c>
       <c r="C14">
-        <v>0.02757859794721385</v>
+        <v>0.01675261689600371</v>
       </c>
       <c r="D14">
-        <v>0.07471300514281351</v>
+        <v>0.06881417446771157</v>
       </c>
       <c r="E14">
-        <v>0.01817507557444034</v>
+        <v>0.02973657124853976</v>
       </c>
       <c r="F14">
-        <v>0.3110446740877809</v>
+        <v>0.2994831784136806</v>
       </c>
     </row>
     <row r="15">
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.2071058122093551</v>
+        <v>0.2071058122093547</v>
       </c>
       <c r="C15">
-        <v>0.01031284278747724</v>
+        <v>0.006148602385946278</v>
       </c>
       <c r="D15">
-        <v>0.08073799058055925</v>
+        <v>0.07559297333495515</v>
       </c>
       <c r="E15">
-        <v>0.04886225848732492</v>
+        <v>0.058946306988546</v>
       </c>
       <c r="F15">
-        <v>0.3653493659313853</v>
+        <v>0.3552653174301634</v>
       </c>
     </row>
     <row r="16">
@@ -702,19 +702,19 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.2506914650573609</v>
+        <v>0.2506914650573605</v>
       </c>
       <c r="C16">
-        <v>0.004769617744525112</v>
+        <v>0.001967633563069171</v>
       </c>
       <c r="D16">
-        <v>0.08882854365257147</v>
+        <v>0.08099690378591694</v>
       </c>
       <c r="E16">
-        <v>0.07659071869917686</v>
+        <v>0.09194045077770735</v>
       </c>
       <c r="F16">
-        <v>0.4247922114155449</v>
+        <v>0.4094424793370136</v>
       </c>
     </row>
     <row r="17">
@@ -724,19 +724,19 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.1485134606462764</v>
+        <v>0.148513460646276</v>
       </c>
       <c r="C17">
-        <v>0.03267752713345162</v>
+        <v>0.03239624528980989</v>
       </c>
       <c r="D17">
-        <v>0.06952802024728691</v>
+        <v>0.06941545268300521</v>
       </c>
       <c r="E17">
-        <v>0.01224104504522244</v>
+        <v>0.01246167341704152</v>
       </c>
       <c r="F17">
-        <v>0.2847858762473304</v>
+        <v>0.2845652478755104</v>
       </c>
     </row>
     <row r="18">
@@ -746,19 +746,19 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.007778454801836161</v>
+        <v>-0.007778454801836591</v>
       </c>
       <c r="C18">
-        <v>0.9432316305924235</v>
+        <v>0.9452822678735411</v>
       </c>
       <c r="D18">
-        <v>0.1092345615458268</v>
+        <v>0.1133351077830037</v>
       </c>
       <c r="E18">
-        <v>-0.2218742612986805</v>
+        <v>-0.2299111842404889</v>
       </c>
       <c r="F18">
-        <v>0.2063173516950082</v>
+        <v>0.2143542746368158</v>
       </c>
     </row>
     <row r="19">
@@ -768,19 +768,19 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.04116197565296988</v>
+        <v>0.0411619756529695</v>
       </c>
       <c r="C19">
-        <v>0.4882408695131835</v>
+        <v>0.48825407205041</v>
       </c>
       <c r="D19">
-        <v>0.05938741107690609</v>
+        <v>0.05938921383568196</v>
       </c>
       <c r="E19">
-        <v>-0.0752352111928411</v>
+        <v>-0.07523874453511498</v>
       </c>
       <c r="F19">
-        <v>0.1575591624987809</v>
+        <v>0.157562695841054</v>
       </c>
     </row>
     <row r="20">
@@ -790,19 +790,19 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.004641515026630615</v>
+        <v>0.004641515026630088</v>
       </c>
       <c r="C20">
-        <v>0.9481128131726364</v>
+        <v>0.9477922997106814</v>
       </c>
       <c r="D20">
-        <v>0.0713235981444313</v>
+        <v>0.07088510781508212</v>
       </c>
       <c r="E20">
-        <v>-0.1351501685842625</v>
+        <v>-0.1342907433311695</v>
       </c>
       <c r="F20">
-        <v>0.1444331986375238</v>
+        <v>0.1435737733844297</v>
       </c>
     </row>
     <row r="21">
@@ -812,19 +812,19 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.1790635667249816</v>
+        <v>0.1790635667249811</v>
       </c>
       <c r="C21">
-        <v>0.006869736271686522</v>
+        <v>0.006715264702780388</v>
       </c>
       <c r="D21">
-        <v>0.06624393447705616</v>
+        <v>0.066059414355046</v>
       </c>
       <c r="E21">
-        <v>0.04922784095572041</v>
+        <v>0.04958949374928276</v>
       </c>
       <c r="F21">
-        <v>0.3088992924942429</v>
+        <v>0.3085376397006795</v>
       </c>
     </row>
     <row r="22">
@@ -834,19 +834,19 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.1047040378735833</v>
+        <v>-0.1047040378735838</v>
       </c>
       <c r="C22">
-        <v>0.3696452199266118</v>
+        <v>0.3919322518859254</v>
       </c>
       <c r="D22">
-        <v>0.1167089387530306</v>
+        <v>0.1223008745130529</v>
       </c>
       <c r="E22">
-        <v>-0.3334493545034143</v>
+        <v>-0.34440934719692</v>
       </c>
       <c r="F22">
-        <v>0.1240412787562477</v>
+        <v>0.1350012714497524</v>
       </c>
     </row>
     <row r="23">
@@ -856,19 +856,19 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.09478125879217578</v>
+        <v>-0.0947812587921763</v>
       </c>
       <c r="C23">
-        <v>0.2916106422054556</v>
+        <v>0.3555261609484517</v>
       </c>
       <c r="D23">
-        <v>0.08987456677434041</v>
+        <v>0.1025856162013687</v>
       </c>
       <c r="E23">
-        <v>-0.2709321727960231</v>
+        <v>-0.2958453718787076</v>
       </c>
       <c r="F23">
-        <v>0.08136965521167155</v>
+        <v>0.106282854294355</v>
       </c>
     </row>
     <row r="24">
@@ -878,19 +878,19 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.01836104189535049</v>
+        <v>0.01836104189535001</v>
       </c>
       <c r="C24">
-        <v>0.8042179862231298</v>
+        <v>0.8045230528286922</v>
       </c>
       <c r="D24">
-        <v>0.07406872131355759</v>
+        <v>0.07418671012519573</v>
       </c>
       <c r="E24">
-        <v>-0.1268109842601566</v>
+        <v>-0.1270422380815465</v>
       </c>
       <c r="F24">
-        <v>0.1635330680508576</v>
+        <v>0.1637643218722466</v>
       </c>
     </row>
     <row r="25">
@@ -900,19 +900,19 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.04906584682091175</v>
+        <v>0.04906584682091122</v>
       </c>
       <c r="C25">
-        <v>0.5392330991196179</v>
+        <v>0.5524334932652031</v>
       </c>
       <c r="D25">
-        <v>0.07991530302471707</v>
+        <v>0.08258609225167381</v>
       </c>
       <c r="E25">
-        <v>-0.1075652689211385</v>
+        <v>-0.1127999196162718</v>
       </c>
       <c r="F25">
-        <v>0.205696962562962</v>
+        <v>0.2109316132580943</v>
       </c>
     </row>
     <row r="26">
@@ -922,19 +922,19 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.05849602500788819</v>
+        <v>0.05849602500788766</v>
       </c>
       <c r="C26">
-        <v>0.410346781494761</v>
+        <v>0.4335297636365809</v>
       </c>
       <c r="D26">
-        <v>0.07105210221181812</v>
+        <v>0.07469175245058285</v>
       </c>
       <c r="E26">
-        <v>-0.08076353635313399</v>
+        <v>-0.087897119737436</v>
       </c>
       <c r="F26">
-        <v>0.1977555863689104</v>
+        <v>0.2048891697532113</v>
       </c>
     </row>
     <row r="27">
@@ -944,19 +944,19 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.03854579147934353</v>
+        <v>0.03854579147934298</v>
       </c>
       <c r="C27">
-        <v>0.5691016230899264</v>
+        <v>0.5868363153170064</v>
       </c>
       <c r="D27">
-        <v>0.06769841651525586</v>
+        <v>0.0709310366702022</v>
       </c>
       <c r="E27">
-        <v>-0.0941406667009495</v>
+        <v>-0.1004764857803432</v>
       </c>
       <c r="F27">
-        <v>0.1712322496596366</v>
+        <v>0.1775680687390291</v>
       </c>
     </row>
     <row r="28">
@@ -966,19 +966,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.1064703671522018</v>
+        <v>-0.1064703671522025</v>
       </c>
       <c r="C28">
-        <v>0.1501385879781683</v>
+        <v>0.1523928554379177</v>
       </c>
       <c r="D28">
-        <v>0.07398697043790742</v>
+        <v>0.07439599464025963</v>
       </c>
       <c r="E28">
-        <v>-0.25148216453573</v>
+        <v>-0.2522838372411462</v>
       </c>
       <c r="F28">
-        <v>0.03854143023132631</v>
+        <v>0.03934310293674123</v>
       </c>
     </row>
     <row r="29">
@@ -988,19 +988,19 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.0261470924793779</v>
+        <v>0.02614709247937754</v>
       </c>
       <c r="C29">
-        <v>0.7435877860830744</v>
+        <v>0.7444593622999958</v>
       </c>
       <c r="D29">
-        <v>0.07993463925929283</v>
+        <v>0.08021719036206337</v>
       </c>
       <c r="E29">
-        <v>-0.1305219215860374</v>
+        <v>-0.1310757115712602</v>
       </c>
       <c r="F29">
-        <v>0.1828161065447932</v>
+        <v>0.1833698965300153</v>
       </c>
     </row>
     <row r="30">
@@ -1010,19 +1010,19 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.007831529061981608</v>
+        <v>0.007831529061981018</v>
       </c>
       <c r="C30">
-        <v>0.9093794835148126</v>
+        <v>0.9111985882830598</v>
       </c>
       <c r="D30">
-        <v>0.06880550194865469</v>
+        <v>0.07022102947977756</v>
       </c>
       <c r="E30">
-        <v>-0.127024776695582</v>
+        <v>-0.1297991596757084</v>
       </c>
       <c r="F30">
-        <v>0.1426878348195453</v>
+        <v>0.1454622177996704</v>
       </c>
     </row>
     <row r="31">
@@ -1032,19 +1032,19 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.119180808937487</v>
+        <v>-0.1191808089374878</v>
       </c>
       <c r="C31">
-        <v>0.1545117294292209</v>
+        <v>0.18917221186094</v>
       </c>
       <c r="D31">
-        <v>0.08370763783894412</v>
+        <v>0.09076764421724899</v>
       </c>
       <c r="E31">
-        <v>-0.2832447643327397</v>
+        <v>-0.297082122564841</v>
       </c>
       <c r="F31">
-        <v>0.04488314645776567</v>
+        <v>0.05872050468986548</v>
       </c>
     </row>
     <row r="32">
@@ -1054,19 +1054,19 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.03671931020065655</v>
+        <v>-0.03671931020065702</v>
       </c>
       <c r="C32">
-        <v>0.6800402825610832</v>
+        <v>0.6984257513778145</v>
       </c>
       <c r="D32">
-        <v>0.08903633265437344</v>
+        <v>0.09477261697399694</v>
       </c>
       <c r="E32">
-        <v>-0.211227315518756</v>
+        <v>-0.2224702261903004</v>
       </c>
       <c r="F32">
-        <v>0.1377886951174429</v>
+        <v>0.1490316057889863</v>
       </c>
     </row>
     <row r="33">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.179625732253813</v>
+        <v>-0.1796257322538136</v>
       </c>
       <c r="C33">
-        <v>0.04074845767094293</v>
+        <v>0.05136955517392705</v>
       </c>
       <c r="D33">
-        <v>0.08779016174260687</v>
+        <v>0.09219236813702833</v>
       </c>
       <c r="E33">
-        <v>-0.3516912874662684</v>
+        <v>-0.3603194534518471</v>
       </c>
       <c r="F33">
-        <v>-0.007560177041357447</v>
+        <v>0.001067988944219916</v>
       </c>
     </row>
     <row r="34">
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.006189517062913981</v>
+        <v>0.00618951706291333</v>
       </c>
       <c r="C34">
-        <v>0.9289153509102932</v>
+        <v>0.9333014810468925</v>
       </c>
       <c r="D34">
-        <v>0.06938175213954306</v>
+        <v>0.07395607988295386</v>
       </c>
       <c r="E34">
-        <v>-0.1297962183148752</v>
+        <v>-0.1387617359454434</v>
       </c>
       <c r="F34">
-        <v>0.1421752524407032</v>
+        <v>0.1511407700712701</v>
       </c>
     </row>
     <row r="35">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.1110991427229713</v>
+        <v>0.1110991427229709</v>
       </c>
       <c r="C35">
-        <v>0.2113579548733775</v>
+        <v>0.1758526132818163</v>
       </c>
       <c r="D35">
-        <v>0.08889068323036037</v>
+        <v>0.08207462174430261</v>
       </c>
       <c r="E35">
-        <v>-0.06312339496969346</v>
+        <v>-0.04976415994061015</v>
       </c>
       <c r="F35">
-        <v>0.2853216804156361</v>
+        <v>0.2719624453865519</v>
       </c>
     </row>
     <row r="36">
@@ -1142,19 +1142,19 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.06020944550704038</v>
+        <v>-0.06020944550704097</v>
       </c>
       <c r="C36">
-        <v>0.4608122635768872</v>
+        <v>0.4658123765802133</v>
       </c>
       <c r="D36">
-        <v>0.08163881902580254</v>
+        <v>0.08255678476591191</v>
       </c>
       <c r="E36">
-        <v>-0.2202185905379966</v>
+        <v>-0.2220177703276532</v>
       </c>
       <c r="F36">
-        <v>0.09979969952391587</v>
+        <v>0.1015988793135713</v>
       </c>
     </row>
     <row r="37">
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.01061718303851512</v>
+        <v>0.01061718303851453</v>
       </c>
       <c r="C37">
-        <v>0.8883452591877181</v>
+        <v>0.8832039177705453</v>
       </c>
       <c r="D37">
-        <v>0.0756218489883058</v>
+        <v>0.07227051728555996</v>
       </c>
       <c r="E37">
-        <v>-0.1375989174228909</v>
+        <v>-0.1310304279852624</v>
       </c>
       <c r="F37">
-        <v>0.1588332834999212</v>
+        <v>0.1522647940622914</v>
       </c>
     </row>
     <row r="38">
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.02796539771514198</v>
+        <v>-0.02796539771514267</v>
       </c>
       <c r="C38">
-        <v>0.7259148791790706</v>
+        <v>0.7255589268420306</v>
       </c>
       <c r="D38">
-        <v>0.07977240982670146</v>
+        <v>0.07966459674799645</v>
       </c>
       <c r="E38">
-        <v>-0.1843164479354459</v>
+        <v>-0.1841051381841224</v>
       </c>
       <c r="F38">
-        <v>0.1283856525051619</v>
+        <v>0.128174342753837</v>
       </c>
     </row>
     <row r="39">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.07170392484158702</v>
+        <v>0.07170392484158639</v>
       </c>
       <c r="C39">
-        <v>0.3230329019769242</v>
+        <v>0.3049416360664359</v>
       </c>
       <c r="D39">
-        <v>0.07255686451604779</v>
+        <v>0.06989409961885083</v>
       </c>
       <c r="E39">
-        <v>-0.07050491644101881</v>
+        <v>-0.06528599314321593</v>
       </c>
       <c r="F39">
-        <v>0.2139127661241929</v>
+        <v>0.2086938428263887</v>
       </c>
     </row>
     <row r="40">
@@ -1230,19 +1230,19 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.0737289477515511</v>
+        <v>0.07372894775155042</v>
       </c>
       <c r="C40">
-        <v>0.4211093860786144</v>
+        <v>0.4085146811314351</v>
       </c>
       <c r="D40">
-        <v>0.09164589811503497</v>
+        <v>0.08920511734125676</v>
       </c>
       <c r="E40">
-        <v>-0.1058937118847446</v>
+        <v>-0.1011098694739822</v>
       </c>
       <c r="F40">
-        <v>0.2533516073878468</v>
+        <v>0.248567764977083</v>
       </c>
     </row>
     <row r="41">
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.02183666294873858</v>
+        <v>0.02183666294873813</v>
       </c>
       <c r="C41">
-        <v>0.7801496449369067</v>
+        <v>0.7611488649331157</v>
       </c>
       <c r="D41">
-        <v>0.07823283149010224</v>
+        <v>0.07183763362662375</v>
       </c>
       <c r="E41">
-        <v>-0.1314968691804528</v>
+        <v>-0.1189625116940279</v>
       </c>
       <c r="F41">
-        <v>0.1751701950779299</v>
+        <v>0.1626358375915041</v>
       </c>
     </row>
     <row r="42">
@@ -1274,19 +1274,19 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.02634495954586608</v>
+        <v>-0.02634495954586668</v>
       </c>
       <c r="C42">
-        <v>0.7922785698607757</v>
+        <v>0.7860294555985776</v>
       </c>
       <c r="D42">
-        <v>0.1000367071942055</v>
+        <v>0.09704551179005101</v>
       </c>
       <c r="E42">
-        <v>-0.2224133027784878</v>
+        <v>-0.2165506675156238</v>
       </c>
       <c r="F42">
-        <v>0.1697233836867556</v>
+        <v>0.1638607484238904</v>
       </c>
     </row>
     <row r="43">
@@ -1296,19 +1296,19 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.1742505487777836</v>
+        <v>0.174250548777783</v>
       </c>
       <c r="C43">
-        <v>0.08293285452456556</v>
+        <v>0.08781880662021879</v>
       </c>
       <c r="D43">
-        <v>0.1004953370842045</v>
+        <v>0.1020789491341195</v>
       </c>
       <c r="E43">
-        <v>-0.02271669252146966</v>
+        <v>-0.02582051510478725</v>
       </c>
       <c r="F43">
-        <v>0.3712177900770369</v>
+        <v>0.3743216126603532</v>
       </c>
     </row>
     <row r="44">
@@ -1318,19 +1318,19 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.04141485948461091</v>
+        <v>0.0414148594846103</v>
       </c>
       <c r="C44">
-        <v>0.6397558471193969</v>
+        <v>0.6604928657990483</v>
       </c>
       <c r="D44">
-        <v>0.08848569012806398</v>
+        <v>0.09428908799990166</v>
       </c>
       <c r="E44">
-        <v>-0.1320139063135659</v>
+        <v>-0.1433883571303247</v>
       </c>
       <c r="F44">
-        <v>0.2148436252827877</v>
+        <v>0.2262180760995453</v>
       </c>
     </row>
     <row r="45">
@@ -1340,19 +1340,19 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.1112480897578255</v>
+        <v>-0.1112480897578261</v>
       </c>
       <c r="C45">
-        <v>0.2168173142753109</v>
+        <v>0.2023433288254417</v>
       </c>
       <c r="D45">
-        <v>0.09007683994197788</v>
+        <v>0.08725999433119916</v>
       </c>
       <c r="E45">
-        <v>-0.2877954518852811</v>
+        <v>-0.2822745359381457</v>
       </c>
       <c r="F45">
-        <v>0.06529927236963011</v>
+        <v>0.05977835642249345</v>
       </c>
     </row>
     <row r="46">
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.03954148760345653</v>
+        <v>-0.03954148760345698</v>
       </c>
       <c r="C46">
-        <v>0.5966037430765647</v>
+        <v>0.5859238371348117</v>
       </c>
       <c r="D46">
-        <v>0.0747065475042258</v>
+        <v>0.07258616825918975</v>
       </c>
       <c r="E46">
-        <v>-0.1859636301210697</v>
+        <v>-0.1818077631672332</v>
       </c>
       <c r="F46">
-        <v>0.1068806549141566</v>
+        <v>0.1027247879603193</v>
       </c>
     </row>
     <row r="47">
@@ -1384,19 +1384,19 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.06168922698429445</v>
+        <v>-0.06168922698429405</v>
       </c>
       <c r="C47">
-        <v>0.548975561450437</v>
+        <v>0.5528570207005812</v>
       </c>
       <c r="D47">
-        <v>0.1029361687472262</v>
+        <v>0.1039441425699456</v>
       </c>
       <c r="E47">
-        <v>-0.2634404104353952</v>
+        <v>-0.2654160028252839</v>
       </c>
       <c r="F47">
-        <v>0.1400619564668063</v>
+        <v>0.1420375488566958</v>
       </c>
     </row>
     <row r="48">
@@ -1406,19 +1406,19 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.02984671870133286</v>
+        <v>-0.02984671870133266</v>
       </c>
       <c r="C48">
-        <v>0.7210497466395989</v>
+        <v>0.7185255517575058</v>
       </c>
       <c r="D48">
-        <v>0.08359109905364194</v>
+        <v>0.08280862823417853</v>
       </c>
       <c r="E48">
-        <v>-0.1936822622745912</v>
+        <v>-0.1921486476494892</v>
       </c>
       <c r="F48">
-        <v>0.1339888248719255</v>
+        <v>0.1324552102468239</v>
       </c>
     </row>
     <row r="49">
@@ -1428,19 +1428,19 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.05445476903451946</v>
+        <v>0.05445476903451948</v>
       </c>
       <c r="C49">
-        <v>0.5428237209823477</v>
+        <v>0.5336756848785287</v>
       </c>
       <c r="D49">
-        <v>0.08948303252846124</v>
+        <v>0.08749091217888845</v>
       </c>
       <c r="E49">
-        <v>-0.1209287519486906</v>
+        <v>-0.1170242678106586</v>
       </c>
       <c r="F49">
-        <v>0.2298382900177295</v>
+        <v>0.2259338058796976</v>
       </c>
     </row>
     <row r="50">
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.02944323281537525</v>
+        <v>-0.0294432328153744</v>
       </c>
       <c r="C50">
-        <v>0.804533565635607</v>
+        <v>0.7953324969346491</v>
       </c>
       <c r="D50">
-        <v>0.1189701813867876</v>
+        <v>0.1135084659046152</v>
       </c>
       <c r="E50">
-        <v>-0.2626205035676763</v>
+        <v>-0.2519157379288128</v>
       </c>
       <c r="F50">
-        <v>0.2037340379369258</v>
+        <v>0.193029272298064</v>
       </c>
     </row>
     <row r="51">
@@ -1472,19 +1472,19 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.03981558781553372</v>
+        <v>0.03981558781553446</v>
       </c>
       <c r="C51">
-        <v>0.6597636364539781</v>
+        <v>0.6604273866790009</v>
       </c>
       <c r="D51">
-        <v>0.09044073883099203</v>
+        <v>0.09062938264027158</v>
       </c>
       <c r="E51">
-        <v>-0.1374450030284037</v>
+        <v>-0.1378147381004974</v>
       </c>
       <c r="F51">
-        <v>0.2170761786594712</v>
+        <v>0.2174459137315663</v>
       </c>
     </row>
     <row r="52">
@@ -1494,19 +1494,19 @@
         </is>
       </c>
       <c r="B52">
-        <v>-0.1027978575655005</v>
+        <v>-0.1027978575655002</v>
       </c>
       <c r="C52">
-        <v>0.3417972829279172</v>
+        <v>0.3482859746663722</v>
       </c>
       <c r="D52">
-        <v>0.1081376904960386</v>
+        <v>0.1096020488225572</v>
       </c>
       <c r="E52">
-        <v>-0.3147438363090754</v>
+        <v>-0.3176139258895129</v>
       </c>
       <c r="F52">
-        <v>0.1091481211780744</v>
+        <v>0.1120182107585125</v>
       </c>
     </row>
     <row r="53">
@@ -1516,19 +1516,19 @@
         </is>
       </c>
       <c r="B53">
-        <v>-0.07400052547899534</v>
+        <v>-0.07400052547899515</v>
       </c>
       <c r="C53">
-        <v>0.4544773381202525</v>
+        <v>0.4499754420034232</v>
       </c>
       <c r="D53">
-        <v>0.09893495114545081</v>
+        <v>0.09795478296911406</v>
       </c>
       <c r="E53">
-        <v>-0.2679094665363086</v>
+        <v>-0.2659883722118961</v>
       </c>
       <c r="F53">
-        <v>0.119908415578318</v>
+        <v>0.1179873212539058</v>
       </c>
     </row>
     <row r="54">
@@ -1538,19 +1538,19 @@
         </is>
       </c>
       <c r="B54">
-        <v>-0.1779346886702914</v>
+        <v>-0.1779346886702917</v>
       </c>
       <c r="C54">
-        <v>0.6336365127105585</v>
+        <v>0.6005197218040472</v>
       </c>
       <c r="D54">
-        <v>0.3733302563012724</v>
+        <v>0.3397948568767377</v>
       </c>
       <c r="E54">
-        <v>-0.9096485453598926</v>
+        <v>-0.8439203702806395</v>
       </c>
       <c r="F54">
-        <v>0.5537791680193098</v>
+        <v>0.4880509929400562</v>
       </c>
     </row>
     <row r="55">
@@ -1560,19 +1560,19 @@
         </is>
       </c>
       <c r="B55">
-        <v>-0.2472888956679036</v>
+        <v>-0.247288895667905</v>
       </c>
       <c r="C55">
-        <v>0.6914660198423981</v>
+        <v>0.6749285805914198</v>
       </c>
       <c r="D55">
-        <v>0.6231037120853465</v>
+        <v>0.5896345584926301</v>
       </c>
       <c r="E55">
-        <v>-1.468549729988398</v>
+        <v>-1.402951394353635</v>
       </c>
       <c r="F55">
-        <v>0.9739719386525905</v>
+        <v>0.9083736030178254</v>
       </c>
     </row>
     <row r="56">
@@ -1582,19 +1582,19 @@
         </is>
       </c>
       <c r="B56">
-        <v>-0.2272088539722371</v>
+        <v>-0.2272088539722389</v>
       </c>
       <c r="C56">
-        <v>0.7579465480744672</v>
+        <v>0.7515188174820575</v>
       </c>
       <c r="D56">
-        <v>0.7372639219030231</v>
+        <v>0.7175681527861466</v>
       </c>
       <c r="E56">
-        <v>-1.672219588002913</v>
+        <v>-1.63361658988602</v>
       </c>
       <c r="F56">
-        <v>1.217801880058439</v>
+        <v>1.179198881941543</v>
       </c>
     </row>
     <row r="57">
@@ -1604,19 +1604,19 @@
         </is>
       </c>
       <c r="B57">
-        <v>-0.1012170215941525</v>
+        <v>-0.1012170215941543</v>
       </c>
       <c r="C57">
-        <v>0.898293719342494</v>
+        <v>0.895488205025986</v>
       </c>
       <c r="D57">
-        <v>0.7918895336962669</v>
+        <v>0.7705142899224146</v>
       </c>
       <c r="E57">
-        <v>-1.653291987373052</v>
+        <v>-1.61139727941554</v>
       </c>
       <c r="F57">
-        <v>1.450857944184748</v>
+        <v>1.408963236227231</v>
       </c>
     </row>
     <row r="58">
@@ -1626,19 +1626,19 @@
         </is>
       </c>
       <c r="B58">
-        <v>-0.255221061268445</v>
+        <v>-0.2552210612684478</v>
       </c>
       <c r="C58">
-        <v>0.7509757550391412</v>
+        <v>0.7520140305723775</v>
       </c>
       <c r="D58">
-        <v>0.8042181727378653</v>
+        <v>0.8077003879231659</v>
       </c>
       <c r="E58">
-        <v>-1.831459715547272</v>
+        <v>-1.838284731896883</v>
       </c>
       <c r="F58">
-        <v>1.321017593010382</v>
+        <v>1.327842609359987</v>
       </c>
     </row>
     <row r="59">
@@ -1648,19 +1648,19 @@
         </is>
       </c>
       <c r="B59">
-        <v>-0.2950078999421992</v>
+        <v>-0.2950078999422026</v>
       </c>
       <c r="C59">
-        <v>0.7209852392080434</v>
+        <v>0.7167807767391572</v>
       </c>
       <c r="D59">
-        <v>0.8260232855781976</v>
+        <v>0.8132214167371963</v>
       </c>
       <c r="E59">
-        <v>-1.91398379006691</v>
+        <v>-1.888892588203745</v>
       </c>
       <c r="F59">
-        <v>1.323967990182511</v>
+        <v>1.29887678831934</v>
       </c>
     </row>
     <row r="60">
@@ -1670,19 +1670,19 @@
         </is>
       </c>
       <c r="B60">
-        <v>-0.1859215185278049</v>
+        <v>-0.1859215185278079</v>
       </c>
       <c r="C60">
-        <v>0.8155013564664659</v>
+        <v>0.8098781549153573</v>
       </c>
       <c r="D60">
-        <v>0.7968011418511866</v>
+        <v>0.7727950299343318</v>
       </c>
       <c r="E60">
-        <v>-1.747623059396521</v>
+        <v>-1.700571944630651</v>
       </c>
       <c r="F60">
-        <v>1.375780022340911</v>
+        <v>1.328728907575035</v>
       </c>
     </row>
     <row r="61">
@@ -1692,19 +1692,19 @@
         </is>
       </c>
       <c r="B61">
-        <v>0.02196805068300145</v>
+        <v>0.02196805068299759</v>
       </c>
       <c r="C61">
-        <v>0.979306719173697</v>
+        <v>0.9788560027888269</v>
       </c>
       <c r="D61">
-        <v>0.8469417388243061</v>
+        <v>0.8288837970462523</v>
       </c>
       <c r="E61">
-        <v>-1.638007254416367</v>
+        <v>-1.602614338896464</v>
       </c>
       <c r="F61">
-        <v>1.68194335578237</v>
+        <v>1.646550440262459</v>
       </c>
     </row>
     <row r="62">
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="B62">
-        <v>-0.2540245978300759</v>
+        <v>-0.25402459783008</v>
       </c>
       <c r="C62">
-        <v>0.7669064815464024</v>
+        <v>0.76489895629051</v>
       </c>
       <c r="D62">
-        <v>0.8569643570392907</v>
+        <v>0.8494276057685967</v>
       </c>
       <c r="E62">
-        <v>-1.933643873661609</v>
+        <v>-1.918872112610616</v>
       </c>
       <c r="F62">
-        <v>1.425594678001457</v>
+        <v>1.410822916950456</v>
       </c>
     </row>
     <row r="63">
@@ -1736,19 +1736,19 @@
         </is>
       </c>
       <c r="B63">
-        <v>-0.2237101015053673</v>
+        <v>-0.2237101015053714</v>
       </c>
       <c r="C63">
-        <v>0.8045266013127839</v>
+        <v>0.8022393087945039</v>
       </c>
       <c r="D63">
-        <v>0.9039042583891387</v>
+        <v>0.8932323192905964</v>
       </c>
       <c r="E63">
-        <v>-1.995329893420466</v>
+        <v>-1.974413277142122</v>
       </c>
       <c r="F63">
-        <v>1.547909690409731</v>
+        <v>1.526993074131379</v>
       </c>
     </row>
     <row r="64">
@@ -1758,19 +1758,19 @@
         </is>
       </c>
       <c r="B64">
-        <v>-0.2699417660369308</v>
+        <v>-0.2699417660369356</v>
       </c>
       <c r="C64">
-        <v>0.7859953293132917</v>
+        <v>0.7803032807646852</v>
       </c>
       <c r="D64">
-        <v>0.9942074568250224</v>
+        <v>0.9677974327893606</v>
       </c>
       <c r="E64">
-        <v>-2.218552574575135</v>
+        <v>-2.166789878634405</v>
       </c>
       <c r="F64">
-        <v>1.678669042501273</v>
+        <v>1.626906346560534</v>
       </c>
     </row>
     <row r="65">
@@ -1780,19 +1780,19 @@
         </is>
       </c>
       <c r="B65">
-        <v>-0.1706783614420005</v>
+        <v>-0.170678361442004</v>
       </c>
       <c r="C65">
-        <v>0.7996199310671597</v>
+        <v>0.79603729871712</v>
       </c>
       <c r="D65">
-        <v>0.6723882131381815</v>
+        <v>0.6603182453196382</v>
       </c>
       <c r="E65">
-        <v>-1.488535042822078</v>
+        <v>-1.464878340603179</v>
       </c>
       <c r="F65">
-        <v>1.147178319938076</v>
+        <v>1.123521617719171</v>
       </c>
     </row>
     <row r="66">
@@ -1851,19 +1851,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.198333824883002</v>
+        <v>-0.1983338248830049</v>
       </c>
       <c r="C2">
-        <v>0.7917132149204824</v>
+        <v>0.7869081385655197</v>
       </c>
       <c r="D2">
-        <v>0.7510182266926106</v>
+        <v>0.7336791880421497</v>
       </c>
       <c r="E2">
-        <v>-1.670302500933656</v>
+        <v>-1.636318609652208</v>
       </c>
       <c r="F2">
-        <v>1.273634851167652</v>
+        <v>1.239650959886198</v>
       </c>
     </row>
   </sheetData>
